--- a/ClosedXML.Tests/Resource/Other/Tables/TableColumnStyles-output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/Tables/TableColumnStyles-output.xlsx
@@ -131,7 +131,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
